--- a/excel básico.xlsx
+++ b/excel básico.xlsx
@@ -1,30 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tauani_rockenbach\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tauani_rockenbach\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22B777B-4B74-4D03-B6C8-4DB650CBF45B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="29">
   <si>
     <t>Vendedor</t>
   </si>
@@ -72,12 +87,51 @@
   </si>
   <si>
     <t xml:space="preserve">    </t>
+  </si>
+  <si>
+    <t>ALUNO</t>
+  </si>
+  <si>
+    <t>NOTA1</t>
+  </si>
+  <si>
+    <t>NOTA2</t>
+  </si>
+  <si>
+    <t>NOTA3</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>TAU</t>
+  </si>
+  <si>
+    <t>LUAN</t>
+  </si>
+  <si>
+    <t>CLARA</t>
+  </si>
+  <si>
+    <t>MEDIA</t>
+  </si>
+  <si>
+    <t>STATUS DO ALUNO</t>
+  </si>
+  <si>
+    <t>nota1</t>
+  </si>
+  <si>
+    <t>nota3</t>
+  </si>
+  <si>
+    <t>PROCX</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -103,7 +157,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -125,6 +179,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -157,7 +217,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
@@ -176,6 +236,11 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -192,6 +257,1863 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$E$17</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>TAU</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$F$16:$H$16</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>NOTA1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>NOTA2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NOTA3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$F$17:$H$17</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>7</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-FC66-487D-8634-8C57EE11B047}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$E$18</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>LUAN</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$F$16:$H$16</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>NOTA1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>NOTA2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NOTA3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$F$18:$H$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-FC66-487D-8634-8C57EE11B047}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$E$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>CLARA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$F$16:$H$16</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>NOTA1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>NOTA2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>NOTA3</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$F$19:$H$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-FC66-487D-8634-8C57EE11B047}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="844291024"/>
+        <c:axId val="844293424"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="844291024"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="844293424"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="844293424"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.00" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="pt-BR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="844291024"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="pt-BR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Planilha1!$I$16</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>MEDIA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:cat>
+            <c:strRef>
+              <c:f>Planilha1!$E$17:$E$19</c:f>
+              <c:strCache>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>TAU</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>LUAN</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>CLARA</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Planilha1!$I$17:$I$19</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B184-40D3-A890-0E31B3E8C7DC}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="pt-BR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>147637</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>33337</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Gráfico 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29EB3A49-CF48-7E6A-0F1E-DC207DA909BE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>519112</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>157162</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>452437</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Gráfico 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9B3C86EE-616D-86C2-C7D7-8024A110B4E9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -456,17 +2378,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N13"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="12.42578125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="9" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.140625" customWidth="1"/>
+    <col min="11" max="11" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="17.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -495,7 +2420,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
@@ -524,7 +2449,7 @@
         <v>413382.36000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>3</v>
       </c>
@@ -539,13 +2464,13 @@
       </c>
       <c r="M3" s="14">
         <f ca="1">TODAY()</f>
-        <v>46129</v>
+        <v>46135</v>
       </c>
       <c r="N3" s="14">
         <v>46381</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>4</v>
       </c>
@@ -565,11 +2490,11 @@
       </c>
       <c r="M4" s="15">
         <f ca="1">NOW()</f>
-        <v>46129.864558217596</v>
+        <v>46135.88538472222</v>
       </c>
       <c r="N4" s="15"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
@@ -583,15 +2508,11 @@
       <c r="I5" s="8"/>
       <c r="J5" s="8"/>
       <c r="K5" s="8"/>
-      <c r="L5" t="e">
-        <f>DIATRABALHO</f>
-        <v>#NAME?</v>
-      </c>
       <c r="N5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>6</v>
       </c>
@@ -607,11 +2528,11 @@
       <c r="J6" s="8"/>
       <c r="K6" s="8"/>
       <c r="L6" t="str">
-        <f>RIGHT(N3,3)</f>
-        <v>381</v>
+        <f>RIGHT(N3,5)</f>
+        <v>46381</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>7</v>
       </c>
@@ -623,7 +2544,7 @@
         <v>Sim</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E8" s="6" t="s">
         <v>10</v>
       </c>
@@ -632,19 +2553,19 @@
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E9" s="12">
         <f>IF(F2&gt;G2,(F2-G2),"Não")</f>
         <v>88585.420000000158</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="E11" t="b">
         <f>AND(F2&gt;G2,H2&gt;I2)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D12" s="13" t="s">
         <v>11</v>
       </c>
@@ -653,17 +2574,188 @@
         <v>sim</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="D13" s="13" t="s">
         <v>12</v>
       </c>
       <c r="E13" t="str">
         <f>+IF(OR(G2&gt;H2,G2&gt;I2),"sim","não")</f>
         <v>sim</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E16" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="17"/>
+      <c r="L16" s="17"/>
+      <c r="M16" s="19" t="s">
+        <v>16</v>
+      </c>
+      <c r="N16" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="O16" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="P16" s="19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="17" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="E17" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="F17" s="16">
+        <v>8</v>
+      </c>
+      <c r="G17" s="16">
+        <v>9</v>
+      </c>
+      <c r="H17" s="16">
+        <v>7</v>
+      </c>
+      <c r="I17" s="16">
+        <f>MEDIAN(F17:H17)</f>
+        <v>8</v>
+      </c>
+      <c r="J17" s="1" t="str">
+        <f>IF(I17&gt;=7,"APROVADO",IF(I17&lt;6,"REPROVADO,""EXAME"))</f>
+        <v>APROVADO</v>
+      </c>
+      <c r="K17" s="18"/>
+      <c r="L17" s="17"/>
+      <c r="M17" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="N17" s="1" t="str">
+        <f>VLOOKUP(M17,E:K,6,0)</f>
+        <v>APROVADO</v>
+      </c>
+      <c r="O17" s="1">
+        <f>VLOOKUP(M17,E16:I19,2,0)</f>
+        <v>8</v>
+      </c>
+      <c r="P17" s="1">
+        <f>VLOOKUP(M17,E16:H19,4,0)</f>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="E18" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="16">
+        <v>3</v>
+      </c>
+      <c r="G18" s="16">
+        <v>2</v>
+      </c>
+      <c r="H18" s="16">
+        <v>5</v>
+      </c>
+      <c r="I18" s="16">
+        <f t="shared" ref="I18:I19" si="0">MEDIAN(F18:H18)</f>
+        <v>3</v>
+      </c>
+      <c r="J18" s="1" t="str">
+        <f>IF(I18&gt;=7,"APROVADO",IF(I18&lt;6,"REPROVADO","EXAME"))</f>
+        <v>REPROVADO</v>
+      </c>
+      <c r="M18" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="N18" s="1" t="str">
+        <f t="shared" ref="N18:N19" si="1">VLOOKUP(M18,E:K,6,0)</f>
+        <v>REPROVADO</v>
+      </c>
+      <c r="O18" s="1">
+        <f t="shared" ref="O18:O19" si="2">VLOOKUP(M18,E17:I20,2,0)</f>
+        <v>3</v>
+      </c>
+      <c r="P18" s="1">
+        <f t="shared" ref="P18:P19" si="3">VLOOKUP(M18,E17:H20,4,0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="E19" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="16">
+        <v>9</v>
+      </c>
+      <c r="G19" s="16">
+        <v>2</v>
+      </c>
+      <c r="H19" s="16">
+        <v>6</v>
+      </c>
+      <c r="I19" s="16">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="J19" s="1" t="str">
+        <f>IF(I19&gt;=7,"APROVADO",IF(I19&lt;6,"REPROVADO","EXAME"))</f>
+        <v>EXAME</v>
+      </c>
+      <c r="K19" s="17"/>
+      <c r="L19" s="17"/>
+      <c r="M19" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="N19" s="1" t="str">
+        <f t="shared" si="1"/>
+        <v>EXAME</v>
+      </c>
+      <c r="O19" s="1">
+        <f t="shared" si="2"/>
+        <v>9</v>
+      </c>
+      <c r="P19" s="1">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="D23" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f>_xlfn.XLOOKUP(E17,E:E,J:J)</f>
+        <v>APROVADO</v>
+      </c>
+    </row>
+    <row r="24" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="E24" s="1" t="str">
+        <f t="shared" ref="E24:E25" si="4">_xlfn.XLOOKUP(E18,E:E,J:J)</f>
+        <v>REPROVADO</v>
+      </c>
+    </row>
+    <row r="25" spans="4:16" x14ac:dyDescent="0.25">
+      <c r="E25" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v>EXAME</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>